--- a/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>63960</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>21</v>
@@ -576,7 +576,7 @@
         <v>63090</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>23</v>
@@ -614,7 +614,7 @@
         <v>39810</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>22</v>
@@ -652,7 +652,7 @@
         <v>29490</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -690,7 +690,7 @@
         <v>28920</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
@@ -728,7 +728,7 @@
         <v>31950</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
@@ -766,7 +766,7 @@
         <v>25380</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -804,7 +804,7 @@
         <v>41250</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
@@ -842,7 +842,7 @@
         <v>21120</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>8</v>
@@ -880,7 +880,7 @@
         <v>24090</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
@@ -918,7 +918,7 @@
         <v>7080</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
@@ -994,7 +994,7 @@
         <v>5940</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -1108,7 +1108,7 @@
         <v>690</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>3450</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         <v>5910</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -2040,7 +2040,7 @@
         <v>690</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>3450</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -2858,7 +2858,7 @@
         <v>5910</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -2972,7 +2972,7 @@
         <v>690</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>954442.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>116666</v>
@@ -3790,7 +3790,7 @@
         <v>1635001.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J16" t="n">
         <v>116666</v>
@@ -3904,7 +3904,7 @@
         <v>190888.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
         <v>5910</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -9934,7 +9934,7 @@
         <v>3480</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -9972,7 +9972,7 @@
         <v>3570</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -10010,7 +10010,7 @@
         <v>6120</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -10048,7 +10048,7 @@
         <v>2220</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -10086,7 +10086,7 @@
         <v>4710</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -10124,7 +10124,7 @@
         <v>15450</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -10162,7 +10162,7 @@
         <v>6210</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -10200,7 +10200,7 @@
         <v>720</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -10314,7 +10314,7 @@
         <v>30</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>22712.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>6.9</v>
@@ -10866,7 +10866,7 @@
         <v>22691.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>11</v>
@@ -10904,7 +10904,7 @@
         <v>21527.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -10942,7 +10942,7 @@
         <v>24582</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="J8" t="n">
         <v>17</v>
@@ -10980,7 +10980,7 @@
         <v>31950</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>6.65</v>
@@ -11018,7 +11018,7 @@
         <v>25380</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
         <v>41250</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
@@ -11094,7 +11094,7 @@
         <v>21120</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>8</v>
@@ -11132,7 +11132,7 @@
         <v>24090</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
@@ -11170,7 +11170,7 @@
         <v>7080</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
@@ -11246,7 +11246,7 @@
         <v>5940</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -11360,7 +11360,7 @@
         <v>690</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2127.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0.9</v>
@@ -11798,7 +11798,7 @@
         <v>1983.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -11836,7 +11836,7 @@
         <v>2606.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>4.2</v>
@@ -11874,7 +11874,7 @@
         <v>5202</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
         <v>8.5</v>
@@ -11912,7 +11912,7 @@
         <v>2220</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -11950,7 +11950,7 @@
         <v>4710</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -11988,7 +11988,7 @@
         <v>15450</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -12026,7 +12026,7 @@
         <v>6210</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -12064,7 +12064,7 @@
         <v>720</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>30</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>588600.54</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>52499.7</v>
@@ -12730,7 +12730,7 @@
         <v>548762.9399999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -12768,7 +12768,7 @@
         <v>720977.5600000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>244998.6</v>
@@ -12806,7 +12806,7 @@
         <v>1439133.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1379988</v>
       </c>
       <c r="J8" t="n">
         <v>495830.5</v>
@@ -12844,7 +12844,7 @@
         <v>614163</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>221665.4</v>
@@ -12882,7 +12882,7 @@
         <v>1303021.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1471987.2</v>
       </c>
       <c r="J10" t="n">
         <v>116666</v>
@@ -12920,7 +12920,7 @@
         <v>4274242.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>349998</v>
@@ -12958,7 +12958,7 @@
         <v>1717996.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J12" t="n">
         <v>58333</v>
@@ -12996,7 +12996,7 @@
         <v>199188</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J13" t="n">
         <v>58333</v>
@@ -13110,7 +13110,7 @@
         <v>8299.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>21330</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -16420,7 +16420,7 @@
         <v>6283385.46</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>402497.7</v>
@@ -16458,7 +16458,7 @@
         <v>6277658.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>536662</v>
       </c>
       <c r="J6" t="n">
         <v>641663</v>
@@ -16496,7 +16496,7 @@
         <v>5955638.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -16534,7 +16534,7 @@
         <v>6800610.3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1931983.2</v>
       </c>
       <c r="J8" t="n">
         <v>991661</v>
@@ -16572,7 +16572,7 @@
         <v>8838967.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>387914.45</v>
@@ -16610,7 +16610,7 @@
         <v>7021377</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1471987.2</v>
       </c>
       <c r="J10" t="n">
         <v>583330</v>
@@ -16648,7 +16648,7 @@
         <v>11411812.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>641663</v>
@@ -16686,7 +16686,7 @@
         <v>5842848</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J12" t="n">
         <v>466664</v>
@@ -16724,7 +16724,7 @@
         <v>6664498.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J13" t="n">
         <v>408331</v>
@@ -16762,7 +16762,7 @@
         <v>1958682</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>349998</v>
@@ -16838,7 +16838,7 @@
         <v>1643301</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J16" t="n">
         <v>233332</v>
@@ -16952,7 +16952,7 @@
         <v>190888.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -17466,7 +17466,7 @@
         <v>1620</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -17656,7 +17656,7 @@
         <v>18360</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -18398,7 +18398,7 @@
         <v>1377</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -18588,7 +18588,7 @@
         <v>18360</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -19330,7 +19330,7 @@
         <v>380947.05</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -19520,7 +19520,7 @@
         <v>5079294</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>291665</v>
@@ -20186,7 +20186,7 @@
         <v>13920</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>13</v>
@@ -21118,7 +21118,7 @@
         <v>7934.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>6.5</v>
@@ -22050,7 +22050,7 @@
         <v>2195051.76</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>379164.5</v>

--- a/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="L4" t="n">
         <v>1176330</v>
@@ -582,7 +582,7 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="L5" t="n">
         <v>1201140</v>
@@ -620,7 +620,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
         <v>689160</v>
@@ -658,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="L7" t="n">
         <v>449940</v>
@@ -696,7 +696,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="L8" t="n">
         <v>415290</v>
@@ -734,7 +734,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="L9" t="n">
         <v>365430</v>
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="L10" t="n">
         <v>389430</v>
@@ -810,7 +810,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="L11" t="n">
         <v>405930</v>
@@ -848,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="L12" t="n">
         <v>400470</v>
@@ -886,7 +886,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
         <v>405060</v>
@@ -924,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
         <v>396990</v>
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="L15" t="n">
         <v>307530</v>
@@ -1000,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L16" t="n">
         <v>177000</v>
@@ -1038,7 +1038,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L17" t="n">
         <v>135030</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L18" t="n">
         <v>62430</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
         <v>29250</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>12870</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>4320</v>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>4170</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>12630</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>13020</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>10650</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>11010</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>13710</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>12060</v>
@@ -1704,7 +1704,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>16470</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L11" t="n">
         <v>22320</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>30510</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>40830</v>
@@ -1856,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
         <v>48960</v>
@@ -1894,7 +1894,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>46920</v>
@@ -1932,7 +1932,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L16" t="n">
         <v>74580</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
         <v>91350</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L18" t="n">
         <v>48630</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>22920</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
         <v>10200</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>3270</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>3330</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="L5" t="n">
         <v>2734.2</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="L6" t="n">
         <v>3940.5</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>6606</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>9734.1</v>
@@ -2598,7 +2598,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>9768.6</v>
@@ -2636,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>14658.3</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L11" t="n">
         <v>22320</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>30510</v>
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>40830</v>
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
         <v>48960</v>
@@ -2826,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>46920</v>
@@ -2864,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L16" t="n">
         <v>74580</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
         <v>91350</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L18" t="n">
         <v>48630</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>22920</v>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
         <v>10200</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>3270</v>
@@ -3130,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>3330</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>53761.68</v>
       </c>
       <c r="L5" t="n">
         <v>25756.16</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>97069.7</v>
       </c>
       <c r="L6" t="n">
         <v>37119.51</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>62228.52</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L8" t="n">
         <v>91695.22</v>
@@ -3530,7 +3530,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L9" t="n">
         <v>92020.21000000001</v>
@@ -3568,7 +3568,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L10" t="n">
         <v>138081.19</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>341344</v>
       </c>
       <c r="L11" t="n">
         <v>210254.4</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L12" t="n">
         <v>287404.2</v>
@@ -3682,7 +3682,7 @@
         <v>58333</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L13" t="n">
         <v>384618.6</v>
@@ -3720,7 +3720,7 @@
         <v>116666</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>426680</v>
       </c>
       <c r="L14" t="n">
         <v>461203.2</v>
@@ -3758,7 +3758,7 @@
         <v>174999</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L15" t="n">
         <v>441986.4</v>
@@ -3796,7 +3796,7 @@
         <v>116666</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L16" t="n">
         <v>702543.6</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>960030</v>
       </c>
       <c r="L17" t="n">
         <v>860517</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L18" t="n">
         <v>458094.6</v>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L19" t="n">
         <v>215906.4</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L20" t="n">
         <v>96084</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L21" t="n">
         <v>30803.4</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L23" t="n">
         <v>31368.6</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
         <v>213750</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L5" t="n">
         <v>156690</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
         <v>68970</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
         <v>24360</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>9720</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>7050</v>
@@ -4500,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>840</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>45.36</v>
       </c>
       <c r="L5" t="n">
         <v>32904.9</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
         <v>25518.9</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="L7" t="n">
         <v>14616</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>6901.2</v>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>5710.5</v>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>747.6</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>967710.24</v>
       </c>
       <c r="L5" t="n">
         <v>309964.16</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L6" t="n">
         <v>240388.04</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>332383.72</v>
       </c>
       <c r="L7" t="n">
         <v>137682.72</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>172805.4</v>
       </c>
       <c r="L8" t="n">
         <v>65009.3</v>
@@ -6326,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L9" t="n">
         <v>53792.91</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L10" t="n">
         <v>7042.39</v>
@@ -7068,7 +7068,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="L4" t="n">
         <v>197940</v>
@@ -7106,7 +7106,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
         <v>143070</v>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L6" t="n">
         <v>41250</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
         <v>14310</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>4710</v>
@@ -7258,7 +7258,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>750</v>
@@ -8038,7 +8038,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60.48</v>
       </c>
       <c r="L5" t="n">
         <v>30044.7</v>
@@ -8076,7 +8076,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>43.55</v>
       </c>
       <c r="L6" t="n">
         <v>15262.5</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="L7" t="n">
         <v>8586</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>3344.1</v>
@@ -8190,7 +8190,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>607.5</v>
@@ -8970,7 +8970,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1290280.32</v>
       </c>
       <c r="L5" t="n">
         <v>283021.07</v>
@@ -9008,7 +9008,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>929095.7</v>
       </c>
       <c r="L6" t="n">
         <v>143772.75</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>332383.72</v>
       </c>
       <c r="L7" t="n">
         <v>80880.12</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>31501.42</v>
@@ -9122,7 +9122,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L9" t="n">
         <v>5722.65</v>
@@ -9864,7 +9864,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>62910</v>
@@ -9902,7 +9902,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L5" t="n">
         <v>107550</v>
@@ -9940,7 +9940,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L6" t="n">
         <v>126150</v>
@@ -9978,7 +9978,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L7" t="n">
         <v>92550</v>
@@ -10016,7 +10016,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L8" t="n">
         <v>102810</v>
@@ -10054,7 +10054,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
         <v>99330</v>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L10" t="n">
         <v>108510</v>
@@ -10130,7 +10130,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L11" t="n">
         <v>147540</v>
@@ -10168,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="L12" t="n">
         <v>172410</v>
@@ -10206,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L13" t="n">
         <v>123000</v>
@@ -10244,7 +10244,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L14" t="n">
         <v>84540</v>
@@ -10282,7 +10282,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
         <v>43800</v>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>13410</v>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>6240</v>
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>570</v>
@@ -10834,7 +10834,7 @@
         <v>6.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>363.72</v>
       </c>
       <c r="L5" t="n">
         <v>252239.4</v>
@@ -10872,7 +10872,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>336.7</v>
       </c>
       <c r="L6" t="n">
         <v>254989.2</v>
@@ -10910,7 +10910,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>350.96</v>
       </c>
       <c r="L7" t="n">
         <v>269964</v>
@@ -10948,7 +10948,7 @@
         <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>298.8</v>
       </c>
       <c r="L8" t="n">
         <v>294855.9</v>
@@ -10986,7 +10986,7 @@
         <v>6.65</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="L9" t="n">
         <v>295998.3</v>
@@ -11024,7 +11024,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="L10" t="n">
         <v>346592.7</v>
@@ -11062,7 +11062,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="L11" t="n">
         <v>405930</v>
@@ -11100,7 +11100,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="L12" t="n">
         <v>400470</v>
@@ -11138,7 +11138,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
         <v>405060</v>
@@ -11176,7 +11176,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
         <v>396990</v>
@@ -11214,7 +11214,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="L15" t="n">
         <v>307530</v>
@@ -11252,7 +11252,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L16" t="n">
         <v>177000</v>
@@ -11290,7 +11290,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L17" t="n">
         <v>135030</v>
@@ -11328,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L18" t="n">
         <v>62430</v>
@@ -11366,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
         <v>29250</v>
@@ -11404,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>12870</v>
@@ -11442,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>4320</v>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>4170</v>
@@ -11766,7 +11766,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="L5" t="n">
         <v>22585.5</v>
@@ -11804,7 +11804,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>46675.5</v>
@@ -11842,7 +11842,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>107.42</v>
       </c>
       <c r="L7" t="n">
         <v>55530</v>
@@ -11880,7 +11880,7 @@
         <v>8.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L8" t="n">
         <v>72995.10000000001</v>
@@ -11918,7 +11918,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
         <v>80457.3</v>
@@ -11956,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L10" t="n">
         <v>96573.89999999999</v>
@@ -11994,7 +11994,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L11" t="n">
         <v>147540</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="L12" t="n">
         <v>172410</v>
@@ -12070,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L13" t="n">
         <v>123000</v>
@@ -12108,7 +12108,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L14" t="n">
         <v>84540</v>
@@ -12146,7 +12146,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
         <v>43800</v>
@@ -12184,7 +12184,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>13410</v>
@@ -12222,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>6240</v>
@@ -12450,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>570</v>
@@ -12698,7 +12698,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1075233.6</v>
       </c>
       <c r="L5" t="n">
         <v>212755.41</v>
@@ -12736,7 +12736,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1927526.9</v>
       </c>
       <c r="L6" t="n">
         <v>439683.21</v>
@@ -12774,7 +12774,7 @@
         <v>244998.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2291698.28</v>
       </c>
       <c r="L7" t="n">
         <v>523092.6</v>
@@ -12812,7 +12812,7 @@
         <v>495830.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2304072</v>
       </c>
       <c r="L8" t="n">
         <v>687613.84</v>
@@ -12850,7 +12850,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2474744</v>
       </c>
       <c r="L9" t="n">
         <v>757907.77</v>
@@ -12888,7 +12888,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2602748</v>
       </c>
       <c r="L10" t="n">
         <v>909726.14</v>
@@ -12926,7 +12926,7 @@
         <v>349998</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2730752</v>
       </c>
       <c r="L11" t="n">
         <v>1389826.8</v>
@@ -12964,7 +12964,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3946790</v>
       </c>
       <c r="L12" t="n">
         <v>1624102.2</v>
@@ -13002,7 +13002,7 @@
         <v>58333</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2837422</v>
       </c>
       <c r="L13" t="n">
         <v>1158660</v>
@@ -13040,7 +13040,7 @@
         <v>116666</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2048064</v>
       </c>
       <c r="L14" t="n">
         <v>796366.8</v>
@@ -13078,7 +13078,7 @@
         <v>116666</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1194704</v>
       </c>
       <c r="L15" t="n">
         <v>412596</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L16" t="n">
         <v>126322.2</v>
@@ -13154,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>58780.8</v>
@@ -13382,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L23" t="n">
         <v>5369.4</v>
@@ -13592,7 +13592,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L4" t="n">
         <v>428220</v>
@@ -13630,7 +13630,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L5" t="n">
         <v>348990</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>89190</v>
@@ -14562,7 +14562,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>40.74</v>
       </c>
       <c r="L5" t="n">
         <v>73287.89999999999</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="L6" t="n">
         <v>33000.3</v>
@@ -15494,7 +15494,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>869147.16</v>
       </c>
       <c r="L5" t="n">
         <v>690372.02</v>
@@ -15532,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>194139.4</v>
       </c>
       <c r="L6" t="n">
         <v>310862.83</v>
@@ -16426,7 +16426,7 @@
         <v>402497.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7759602.48</v>
       </c>
       <c r="L5" t="n">
         <v>2376095.15</v>
@@ -16464,7 +16464,7 @@
         <v>641663</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7183157.8</v>
       </c>
       <c r="L6" t="n">
         <v>2401998.26</v>
@@ -16502,7 +16502,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7487380.64</v>
       </c>
       <c r="L7" t="n">
         <v>2543060.88</v>
@@ -16540,7 +16540,7 @@
         <v>991661</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6374599.2</v>
       </c>
       <c r="L8" t="n">
         <v>2777542.58</v>
@@ -16578,7 +16578,7 @@
         <v>387914.45</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6720210</v>
       </c>
       <c r="L9" t="n">
         <v>2788303.99</v>
@@ -16616,7 +16616,7 @@
         <v>583330</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7189558</v>
       </c>
       <c r="L10" t="n">
         <v>3264903.23</v>
@@ -16654,7 +16654,7 @@
         <v>641663</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6677542</v>
       </c>
       <c r="L11" t="n">
         <v>3823860.6</v>
@@ -16692,7 +16692,7 @@
         <v>466664</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7978916</v>
       </c>
       <c r="L12" t="n">
         <v>3772427.4</v>
@@ -16730,7 +16730,7 @@
         <v>408331</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>7552236</v>
       </c>
       <c r="L13" t="n">
         <v>3815665.2</v>
@@ -16768,7 +16768,7 @@
         <v>349998</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>7082888</v>
       </c>
       <c r="L14" t="n">
         <v>3739645.8</v>
@@ -16806,7 +16806,7 @@
         <v>583330</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6485536</v>
       </c>
       <c r="L15" t="n">
         <v>2896932.6</v>
@@ -16844,7 +16844,7 @@
         <v>233332</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3242768</v>
       </c>
       <c r="L16" t="n">
         <v>1667340</v>
@@ -16882,7 +16882,7 @@
         <v>116666</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1898726</v>
       </c>
       <c r="L17" t="n">
         <v>1271982.6</v>
@@ -16920,7 +16920,7 @@
         <v>58333</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>810692</v>
       </c>
       <c r="L18" t="n">
         <v>588090.6</v>
@@ -16958,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>341344</v>
       </c>
       <c r="L19" t="n">
         <v>275535</v>
@@ -16996,7 +16996,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L20" t="n">
         <v>121235.4</v>
@@ -17034,7 +17034,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L21" t="n">
         <v>40694.4</v>
@@ -17110,7 +17110,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L23" t="n">
         <v>39281.4</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
         <v>41700</v>
@@ -17358,7 +17358,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
         <v>37110</v>
@@ -17396,7 +17396,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
         <v>41640</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
         <v>56580</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="L8" t="n">
         <v>88800</v>
@@ -17510,7 +17510,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L9" t="n">
         <v>131730</v>
@@ -17548,7 +17548,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
         <v>140970</v>
@@ -17586,7 +17586,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L11" t="n">
         <v>168330</v>
@@ -17624,7 +17624,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L12" t="n">
         <v>183600</v>
@@ -17662,7 +17662,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L13" t="n">
         <v>231150</v>
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
         <v>250740</v>
@@ -17738,7 +17738,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L15" t="n">
         <v>211110</v>
@@ -17776,7 +17776,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
         <v>88050</v>
@@ -17814,7 +17814,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L17" t="n">
         <v>37230</v>
@@ -17852,7 +17852,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -17890,7 +17890,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>5490</v>
@@ -17928,7 +17928,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1770</v>
@@ -17966,7 +17966,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>750</v>
@@ -18290,7 +18290,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>7793.1</v>
@@ -18328,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="L6" t="n">
         <v>15406.8</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>57.4</v>
       </c>
       <c r="L7" t="n">
         <v>33948</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>74.7</v>
       </c>
       <c r="L8" t="n">
         <v>63048</v>
@@ -18442,7 +18442,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L9" t="n">
         <v>106701.3</v>
@@ -18480,7 +18480,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
         <v>125463.3</v>
@@ -18518,7 +18518,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L11" t="n">
         <v>168330</v>
@@ -18556,7 +18556,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L12" t="n">
         <v>183600</v>
@@ -18594,7 +18594,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L13" t="n">
         <v>231150</v>
@@ -18632,7 +18632,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
         <v>250740</v>
@@ -18670,7 +18670,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L15" t="n">
         <v>211110</v>
@@ -18708,7 +18708,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
         <v>88050</v>
@@ -18746,7 +18746,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L17" t="n">
         <v>37230</v>
@@ -18784,7 +18784,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>5490</v>
@@ -18860,7 +18860,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1770</v>
@@ -18898,7 +18898,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>750</v>
@@ -19222,7 +19222,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L5" t="n">
         <v>73411</v>
@@ -19260,7 +19260,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>526949.8</v>
       </c>
       <c r="L6" t="n">
         <v>145132.06</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1224571.6</v>
       </c>
       <c r="L7" t="n">
         <v>319790.16</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1593649.8</v>
       </c>
       <c r="L8" t="n">
         <v>593912.16</v>
@@ -19374,7 +19374,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2581414</v>
       </c>
       <c r="L9" t="n">
         <v>1005126.25</v>
@@ -19412,7 +19412,7 @@
         <v>233332</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2794754</v>
       </c>
       <c r="L10" t="n">
         <v>1181864.29</v>
@@ -19450,7 +19450,7 @@
         <v>233332</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3008094</v>
       </c>
       <c r="L11" t="n">
         <v>1585668.6</v>
@@ -19488,7 +19488,7 @@
         <v>408331</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3520110</v>
       </c>
       <c r="L12" t="n">
         <v>1729512</v>
@@ -19526,7 +19526,7 @@
         <v>291665</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4224132</v>
       </c>
       <c r="L13" t="n">
         <v>2177433</v>
@@ -19564,7 +19564,7 @@
         <v>116666</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4586810</v>
       </c>
       <c r="L14" t="n">
         <v>2361970.8</v>
@@ -19602,7 +19602,7 @@
         <v>291665</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4736148</v>
       </c>
       <c r="L15" t="n">
         <v>1988656.2</v>
@@ -19640,7 +19640,7 @@
         <v>116666</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2261404</v>
       </c>
       <c r="L16" t="n">
         <v>829431</v>
@@ -19678,7 +19678,7 @@
         <v>116666</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>874694</v>
       </c>
       <c r="L17" t="n">
         <v>350706.6</v>
@@ -19716,7 +19716,7 @@
         <v>58333</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L18" t="n">
         <v>106822.8</v>
@@ -19754,7 +19754,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L19" t="n">
         <v>51715.8</v>
@@ -19792,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L20" t="n">
         <v>16673.4</v>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L21" t="n">
         <v>7065</v>
@@ -20116,7 +20116,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="L4" t="n">
         <v>199530</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
         <v>344520</v>
@@ -20192,7 +20192,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L6" t="n">
         <v>259440</v>
@@ -20230,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="L7" t="n">
         <v>193530</v>
@@ -20268,7 +20268,7 @@
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="L8" t="n">
         <v>151380</v>
@@ -20306,7 +20306,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L9" t="n">
         <v>68670</v>
@@ -20344,7 +20344,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L10" t="n">
         <v>91770</v>
@@ -20382,7 +20382,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
         <v>43110</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>143.22</v>
       </c>
       <c r="L5" t="n">
         <v>72349.2</v>
@@ -21124,7 +21124,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="L6" t="n">
         <v>95992.8</v>
@@ -21162,7 +21162,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>150.88</v>
       </c>
       <c r="L7" t="n">
         <v>116118</v>
@@ -21200,7 +21200,7 @@
         <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="L8" t="n">
         <v>107479.8</v>
@@ -21238,7 +21238,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L9" t="n">
         <v>55622.7</v>
@@ -21276,7 +21276,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L10" t="n">
         <v>81675.3</v>
@@ -21314,7 +21314,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
         <v>43110</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3055455.48</v>
       </c>
       <c r="L5" t="n">
         <v>681529.46</v>
@@ -22056,7 +22056,7 @@
         <v>379164.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2912091</v>
       </c>
       <c r="L6" t="n">
         <v>904252.1800000001</v>
@@ -22094,7 +22094,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3218873.92</v>
       </c>
       <c r="L7" t="n">
         <v>1093831.56</v>
@@ -22132,7 +22132,7 @@
         <v>297498.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2054464.2</v>
       </c>
       <c r="L8" t="n">
         <v>1012459.72</v>
@@ -22170,7 +22170,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1322708</v>
       </c>
       <c r="L9" t="n">
         <v>523965.83</v>
@@ -22208,7 +22208,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1514714</v>
       </c>
       <c r="L10" t="n">
         <v>769381.33</v>
@@ -22246,7 +22246,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L11" t="n">
         <v>406096.2</v>

--- a/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Present_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>960</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
         <v>1171710</v>
@@ -590,7 +590,7 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>856</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
         <v>1198740</v>
@@ -631,7 +631,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>201</v>
       </c>
       <c r="L6" t="n">
         <v>688170</v>
@@ -672,7 +672,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>408</v>
+        <v>174</v>
       </c>
       <c r="L7" t="n">
         <v>447870</v>
@@ -713,7 +713,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="L8" t="n">
         <v>414000</v>
@@ -754,7 +754,7 @@
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>307</v>
+        <v>148</v>
       </c>
       <c r="L9" t="n">
         <v>365040</v>
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>327</v>
+        <v>139</v>
       </c>
       <c r="L10" t="n">
         <v>389340</v>
@@ -836,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>304</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
         <v>405660</v>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>374</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
         <v>400260</v>
@@ -918,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>354</v>
+        <v>108</v>
       </c>
       <c r="L13" t="n">
         <v>405060</v>
@@ -959,7 +959,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
         <v>396990</v>
@@ -1000,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="L15" t="n">
         <v>307530</v>
@@ -1041,7 +1041,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
         <v>177000</v>
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
         <v>135030</v>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>62430</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>29250</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>12870</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>4320</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>4170</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>12360</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>10770</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>10950</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>13500</v>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>12090</v>
@@ -1799,7 +1799,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>16410</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>22380</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
         <v>30660</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
         <v>41070</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>49020</v>
@@ -2004,7 +2004,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>46920</v>
@@ -2045,7 +2045,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>74940</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>91320</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>48750</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>22950</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>10230</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>3270</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>3330</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0.66</v>
       </c>
       <c r="L5" t="n">
         <v>2595.6</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
         <v>3984.9</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>6570</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.89</v>
+        <v>4.42</v>
       </c>
       <c r="L8" t="n">
         <v>9585</v>
@@ -2762,7 +2762,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>5.62</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>9792.9</v>
@@ -2803,7 +2803,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>10.44</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>14604.9</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>14.38</v>
+        <v>5.39</v>
       </c>
       <c r="L11" t="n">
         <v>22380</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>19.47</v>
+        <v>11.12</v>
       </c>
       <c r="L12" t="n">
         <v>30660</v>
@@ -2926,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>21.84</v>
+        <v>13.29</v>
       </c>
       <c r="L13" t="n">
         <v>41070</v>
@@ -2967,7 +2967,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>19.44</v>
+        <v>2.92</v>
       </c>
       <c r="L14" t="n">
         <v>49020</v>
@@ -3008,7 +3008,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>24.65</v>
+        <v>3.94</v>
       </c>
       <c r="L15" t="n">
         <v>46920</v>
@@ -3049,7 +3049,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>74940</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>91320</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>48750</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>22950</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>10230</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>3270</v>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>3330</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80360.17999999999</v>
+        <v>32144.07</v>
       </c>
       <c r="L5" t="n">
         <v>467208</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>172325.24</v>
+        <v>73853.67999999999</v>
       </c>
       <c r="L6" t="n">
         <v>717282</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
         <v>1182600</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>285897.73</v>
+        <v>214423.3</v>
       </c>
       <c r="L8" t="n">
         <v>1725300</v>
@@ -3766,7 +3766,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>272933.28</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>1762722</v>
@@ -3807,7 +3807,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>506924.64</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>2628882</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>698041.0600000001</v>
+        <v>261765.4</v>
       </c>
       <c r="L11" t="n">
         <v>4028400</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>945239.65</v>
+        <v>540136.9399999999</v>
       </c>
       <c r="L12" t="n">
         <v>5518800</v>
@@ -3930,7 +3930,7 @@
         <v>24278</v>
       </c>
       <c r="K13" t="n">
-        <v>1060390.21</v>
+        <v>645454.91</v>
       </c>
       <c r="L13" t="n">
         <v>7392600</v>
@@ -3971,7 +3971,7 @@
         <v>48556</v>
       </c>
       <c r="K14" t="n">
-        <v>943928.64</v>
+        <v>141589.3</v>
       </c>
       <c r="L14" t="n">
         <v>8823600</v>
@@ -4012,7 +4012,7 @@
         <v>72834</v>
       </c>
       <c r="K15" t="n">
-        <v>1196905.4</v>
+        <v>191504.86</v>
       </c>
       <c r="L15" t="n">
         <v>8445600</v>
@@ -4053,7 +4053,7 @@
         <v>48556</v>
       </c>
       <c r="K16" t="n">
-        <v>1650904</v>
+        <v>194224</v>
       </c>
       <c r="L16" t="n">
         <v>13489200</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2185020</v>
+        <v>339892</v>
       </c>
       <c r="L17" t="n">
         <v>16437600</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1262456</v>
+        <v>97112</v>
       </c>
       <c r="L18" t="n">
         <v>8775000</v>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>631228</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>4131000</v>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1841400</v>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>588600</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>599400</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
         <v>213720</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="L5" t="n">
         <v>157650</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
         <v>69180</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>24330</v>
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>9780</v>
@@ -4770,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>7110</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>35.42</v>
+        <v>18.54</v>
       </c>
       <c r="L5" t="n">
         <v>33106.5</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18.76</v>
+        <v>11.15</v>
       </c>
       <c r="L6" t="n">
         <v>25596.6</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>11.48</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>14598</v>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>6943.8</v>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.02</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>5759.1</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1719707.85</v>
+        <v>900034.02</v>
       </c>
       <c r="L5" t="n">
         <v>5959170</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>910862</v>
+        <v>541593.62</v>
       </c>
       <c r="L6" t="n">
         <v>4607388</v>
@@ -6696,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>557617.1</v>
+        <v>402723.46</v>
       </c>
       <c r="L7" t="n">
         <v>2627640</v>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321634.94</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>1249884</v>
@@ -6778,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>194952.34</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>1036638</v>
@@ -7577,7 +7577,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>268</v>
+        <v>52</v>
       </c>
       <c r="L4" t="n">
         <v>198060</v>
@@ -7618,7 +7618,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>143460</v>
@@ -7659,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="L6" t="n">
         <v>41610</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>14460</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4710</v>
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>750</v>
@@ -8622,7 +8622,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>47.66</v>
+        <v>7.94</v>
       </c>
       <c r="L5" t="n">
         <v>30126.6</v>
@@ -8663,7 +8663,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>33.97</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>15395.7</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.12</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>8676</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>3344.1</v>
@@ -8786,7 +8786,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>607.5</v>
@@ -9626,7 +9626,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2314373.18</v>
+        <v>385728.86</v>
       </c>
       <c r="L5" t="n">
         <v>5422788</v>
@@ -9667,7 +9667,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1649398.76</v>
+        <v>393886.27</v>
       </c>
       <c r="L6" t="n">
         <v>2771226</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>588595.83</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
         <v>1561680</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>601938</v>
@@ -9790,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38990.47</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>109350</v>
@@ -10589,7 +10589,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
         <v>63120</v>
@@ -10630,7 +10630,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="L5" t="n">
         <v>107880</v>
@@ -10671,7 +10671,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="L6" t="n">
         <v>126330</v>
@@ -10712,7 +10712,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
         <v>92520</v>
@@ -10753,7 +10753,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="L8" t="n">
         <v>102750</v>
@@ -10794,7 +10794,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
         <v>99150</v>
@@ -10835,7 +10835,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="L10" t="n">
         <v>108600</v>
@@ -10876,7 +10876,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="L11" t="n">
         <v>147660</v>
@@ -10917,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="L12" t="n">
         <v>172440</v>
@@ -10958,7 +10958,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
         <v>123000</v>
@@ -10999,7 +10999,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>84600</v>
@@ -11040,7 +11040,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>43800</v>
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>13410</v>
@@ -11368,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>570</v>
@@ -11634,7 +11634,7 @@
         <v>6.9</v>
       </c>
       <c r="K5" t="n">
-        <v>283.34</v>
+        <v>102.28</v>
       </c>
       <c r="L5" t="n">
         <v>251735.4</v>
@@ -11675,7 +11675,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>253.5</v>
+        <v>101.91</v>
       </c>
       <c r="L6" t="n">
         <v>254622.9</v>
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>260.3</v>
+        <v>111.01</v>
       </c>
       <c r="L7" t="n">
         <v>268722</v>
@@ -11757,7 +11757,7 @@
         <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>236.26</v>
+        <v>119.23</v>
       </c>
       <c r="L8" t="n">
         <v>293940</v>
@@ -11798,7 +11798,7 @@
         <v>6.65</v>
       </c>
       <c r="K9" t="n">
-        <v>246.52</v>
+        <v>118.84</v>
       </c>
       <c r="L9" t="n">
         <v>295682.4</v>
@@ -11839,7 +11839,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>284.49</v>
+        <v>120.93</v>
       </c>
       <c r="L10" t="n">
         <v>346512.6</v>
@@ -11880,7 +11880,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>273.14</v>
+        <v>114.11</v>
       </c>
       <c r="L11" t="n">
         <v>405660</v>
@@ -11921,7 +11921,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>346.7</v>
+        <v>123.29</v>
       </c>
       <c r="L12" t="n">
         <v>400260</v>
@@ -11962,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>336.12</v>
+        <v>102.55</v>
       </c>
       <c r="L13" t="n">
         <v>405060</v>
@@ -12003,7 +12003,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>322.7</v>
+        <v>97.2</v>
       </c>
       <c r="L14" t="n">
         <v>396990</v>
@@ -12044,7 +12044,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>299.74</v>
+        <v>75.92</v>
       </c>
       <c r="L15" t="n">
         <v>307530</v>
@@ -12085,7 +12085,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
         <v>177000</v>
@@ -12126,7 +12126,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
         <v>135030</v>
@@ -12167,7 +12167,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>62430</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>29250</v>
@@ -12249,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>12870</v>
@@ -12290,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>4320</v>
@@ -12372,7 +12372,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>4170</v>
@@ -12638,7 +12638,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>39.72</v>
+        <v>23.83</v>
       </c>
       <c r="L5" t="n">
         <v>22654.8</v>
@@ -12679,7 +12679,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>70.47</v>
+        <v>37.52</v>
       </c>
       <c r="L6" t="n">
         <v>46742.1</v>
@@ -12720,7 +12720,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>83.58</v>
+        <v>47.85</v>
       </c>
       <c r="L7" t="n">
         <v>55512</v>
@@ -12761,7 +12761,7 @@
         <v>8.5</v>
       </c>
       <c r="K8" t="n">
-        <v>88.31999999999999</v>
+        <v>51.52</v>
       </c>
       <c r="L8" t="n">
         <v>72952.5</v>
@@ -12802,7 +12802,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>93.15000000000001</v>
+        <v>48.98</v>
       </c>
       <c r="L9" t="n">
         <v>80311.5</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>106.14</v>
+        <v>59.16</v>
       </c>
       <c r="L10" t="n">
         <v>96654</v>
@@ -12884,7 +12884,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>115.01</v>
+        <v>53.91</v>
       </c>
       <c r="L11" t="n">
         <v>147660</v>
@@ -12925,7 +12925,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>171.5</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>172440</v>
@@ -12966,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>126.28</v>
+        <v>42.73</v>
       </c>
       <c r="L13" t="n">
         <v>123000</v>
@@ -13007,7 +13007,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>93.31</v>
+        <v>33.05</v>
       </c>
       <c r="L14" t="n">
         <v>84600</v>
@@ -13048,7 +13048,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>56.2</v>
+        <v>12.82</v>
       </c>
       <c r="L15" t="n">
         <v>43800</v>
@@ -13089,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>13410</v>
@@ -13376,7 +13376,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>570</v>
@@ -13642,7 +13642,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1928644.32</v>
+        <v>1157186.59</v>
       </c>
       <c r="L5" t="n">
         <v>4077864</v>
@@ -13683,7 +13683,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>3421886.99</v>
+        <v>1821724.01</v>
       </c>
       <c r="L6" t="n">
         <v>8413578</v>
@@ -13724,7 +13724,7 @@
         <v>101967.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4058213.37</v>
+        <v>2323404.6</v>
       </c>
       <c r="L7" t="n">
         <v>9992160</v>
@@ -13765,7 +13765,7 @@
         <v>206363</v>
       </c>
       <c r="K8" t="n">
-        <v>4288465.92</v>
+        <v>2501605.12</v>
       </c>
       <c r="L8" t="n">
         <v>13131450</v>
@@ -13806,7 +13806,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>4522894.29</v>
+        <v>2378418.55</v>
       </c>
       <c r="L9" t="n">
         <v>14456070</v>
@@ -13847,7 +13847,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>5153733.84</v>
+        <v>2872572.96</v>
       </c>
       <c r="L10" t="n">
         <v>17397720</v>
@@ -13888,7 +13888,7 @@
         <v>145668</v>
       </c>
       <c r="K11" t="n">
-        <v>5584328.45</v>
+        <v>2617653.96</v>
       </c>
       <c r="L11" t="n">
         <v>26578800</v>
@@ -13929,7 +13929,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>8327111.22</v>
+        <v>3240821.66</v>
       </c>
       <c r="L12" t="n">
         <v>31039200</v>
@@ -13970,7 +13970,7 @@
         <v>24278</v>
       </c>
       <c r="K13" t="n">
-        <v>6131821.63</v>
+        <v>2074676.49</v>
       </c>
       <c r="L13" t="n">
         <v>22140000</v>
@@ -14011,7 +14011,7 @@
         <v>48556</v>
       </c>
       <c r="K14" t="n">
-        <v>4530857.47</v>
+        <v>1604678.69</v>
       </c>
       <c r="L14" t="n">
         <v>15228000</v>
@@ -14052,7 +14052,7 @@
         <v>48556</v>
       </c>
       <c r="K15" t="n">
-        <v>2728944.31</v>
+        <v>622390.8100000001</v>
       </c>
       <c r="L15" t="n">
         <v>7884000</v>
@@ -14093,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>582672</v>
+        <v>145668</v>
       </c>
       <c r="L16" t="n">
         <v>2413800</v>
@@ -14380,7 +14380,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>102600</v>
@@ -14605,7 +14605,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="L4" t="n">
         <v>428430</v>
@@ -14646,7 +14646,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="L5" t="n">
         <v>349740</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>91620</v>
@@ -15650,7 +15650,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>32.11</v>
+        <v>13.57</v>
       </c>
       <c r="L5" t="n">
         <v>73445.39999999999</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.1</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>33899.4</v>
@@ -16654,7 +16654,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1558987.49</v>
+        <v>658953.48</v>
       </c>
       <c r="L5" t="n">
         <v>13220172</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>344650.49</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>6101892</v>
@@ -17658,7 +17658,7 @@
         <v>167518.2</v>
       </c>
       <c r="K5" t="n">
-        <v>13757662.82</v>
+        <v>4966259.12</v>
       </c>
       <c r="L5" t="n">
         <v>45312372</v>
@@ -17699,7 +17699,7 @@
         <v>267058</v>
       </c>
       <c r="K6" t="n">
-        <v>12308946</v>
+        <v>4948196.29</v>
       </c>
       <c r="L6" t="n">
         <v>45832122</v>
@@ -17740,7 +17740,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>12639321.02</v>
+        <v>5390298.67</v>
       </c>
       <c r="L7" t="n">
         <v>48369960</v>
@@ -17781,7 +17781,7 @@
         <v>412726</v>
       </c>
       <c r="K8" t="n">
-        <v>11471646.34</v>
+        <v>5789428.99</v>
       </c>
       <c r="L8" t="n">
         <v>52909200</v>
@@ -17822,7 +17822,7 @@
         <v>161448.7</v>
       </c>
       <c r="K9" t="n">
-        <v>11970073.68</v>
+        <v>5770589.26</v>
       </c>
       <c r="L9" t="n">
         <v>53222832</v>
@@ -17863,7 +17863,7 @@
         <v>242780</v>
       </c>
       <c r="K10" t="n">
-        <v>13813696.44</v>
+        <v>5871877.08</v>
       </c>
       <c r="L10" t="n">
         <v>62372268</v>
@@ -17904,7 +17904,7 @@
         <v>267058</v>
       </c>
       <c r="K11" t="n">
-        <v>13262780.06</v>
+        <v>5540700.88</v>
       </c>
       <c r="L11" t="n">
         <v>73018800</v>
@@ -17945,7 +17945,7 @@
         <v>194224</v>
       </c>
       <c r="K12" t="n">
-        <v>16834268.09</v>
+        <v>5986517.8</v>
       </c>
       <c r="L12" t="n">
         <v>72046800</v>
@@ -17986,7 +17986,7 @@
         <v>169946</v>
       </c>
       <c r="K13" t="n">
-        <v>16320788.39</v>
+        <v>4979223.58</v>
       </c>
       <c r="L13" t="n">
         <v>72910800</v>
@@ -18027,7 +18027,7 @@
         <v>145668</v>
       </c>
       <c r="K14" t="n">
-        <v>15669215.42</v>
+        <v>4719643.2</v>
       </c>
       <c r="L14" t="n">
         <v>71458200</v>
@@ -18068,7 +18068,7 @@
         <v>242780</v>
       </c>
       <c r="K15" t="n">
-        <v>14554369.66</v>
+        <v>3686468.63</v>
       </c>
       <c r="L15" t="n">
         <v>55355400</v>
@@ -18109,7 +18109,7 @@
         <v>97112</v>
       </c>
       <c r="K16" t="n">
-        <v>7380512</v>
+        <v>1165344</v>
       </c>
       <c r="L16" t="n">
         <v>31860000</v>
@@ -18150,7 +18150,7 @@
         <v>48556</v>
       </c>
       <c r="K17" t="n">
-        <v>4321484</v>
+        <v>582672</v>
       </c>
       <c r="L17" t="n">
         <v>24305400</v>
@@ -18191,7 +18191,7 @@
         <v>24278</v>
       </c>
       <c r="K18" t="n">
-        <v>1845128</v>
+        <v>97112</v>
       </c>
       <c r="L18" t="n">
         <v>11237400</v>
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>776896</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>5265000</v>
@@ -18273,7 +18273,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>194224</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>2316600</v>
@@ -18314,7 +18314,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>777600</v>
@@ -18396,7 +18396,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>750600</v>
@@ -18621,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>37620</v>
@@ -18662,7 +18662,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
         <v>35430</v>
@@ -18703,7 +18703,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L6" t="n">
         <v>40890</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
         <v>55560</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
         <v>88200</v>
@@ -18826,7 +18826,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
         <v>131580</v>
@@ -18867,7 +18867,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="L10" t="n">
         <v>140940</v>
@@ -18908,7 +18908,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="L11" t="n">
         <v>168300</v>
@@ -18949,7 +18949,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="L12" t="n">
         <v>183420</v>
@@ -18990,7 +18990,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="L13" t="n">
         <v>231210</v>
@@ -19031,7 +19031,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="L14" t="n">
         <v>250800</v>
@@ -19072,7 +19072,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>222</v>
+        <v>60</v>
       </c>
       <c r="L15" t="n">
         <v>211230</v>
@@ -19113,7 +19113,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
         <v>88050</v>
@@ -19154,7 +19154,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>37320</v>
@@ -19195,7 +19195,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -19236,7 +19236,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>5490</v>
@@ -19277,7 +19277,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1770</v>
@@ -19318,7 +19318,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>750</v>
@@ -19666,7 +19666,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9</v>
+        <v>9.27</v>
       </c>
       <c r="L5" t="n">
         <v>7440.3</v>
@@ -19707,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>12.68</v>
+        <v>10.65</v>
       </c>
       <c r="L6" t="n">
         <v>15129.3</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>33.18</v>
+        <v>21.05</v>
       </c>
       <c r="L7" t="n">
         <v>33336</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>54.46</v>
+        <v>36.06</v>
       </c>
       <c r="L8" t="n">
         <v>62622</v>
@@ -19830,7 +19830,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>90.73999999999999</v>
+        <v>48.98</v>
       </c>
       <c r="L9" t="n">
         <v>106579.8</v>
@@ -19871,7 +19871,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>105.27</v>
+        <v>45.24</v>
       </c>
       <c r="L10" t="n">
         <v>125436.6</v>
@@ -19912,7 +19912,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>118.6</v>
+        <v>53.01</v>
       </c>
       <c r="L11" t="n">
         <v>168300</v>
@@ -19953,7 +19953,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>152.96</v>
+        <v>44.5</v>
       </c>
       <c r="L12" t="n">
         <v>183420</v>
@@ -19994,7 +19994,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>188</v>
+        <v>46.53</v>
       </c>
       <c r="L13" t="n">
         <v>231210</v>
@@ -20035,7 +20035,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>208.98</v>
+        <v>61.24</v>
       </c>
       <c r="L14" t="n">
         <v>250800</v>
@@ -20076,7 +20076,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>218.89</v>
+        <v>59.16</v>
       </c>
       <c r="L15" t="n">
         <v>211230</v>
@@ -20117,7 +20117,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
         <v>88050</v>
@@ -20158,7 +20158,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>37320</v>
@@ -20199,7 +20199,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>5490</v>
@@ -20281,7 +20281,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1770</v>
@@ -20322,7 +20322,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>750</v>
@@ -20670,7 +20670,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>675025.51</v>
+        <v>450017.01</v>
       </c>
       <c r="L5" t="n">
         <v>1339254</v>
@@ -20711,7 +20711,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>615447.3</v>
+        <v>516975.73</v>
       </c>
       <c r="L6" t="n">
         <v>2723274</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1610893.86</v>
+        <v>1022298.02</v>
       </c>
       <c r="L7" t="n">
         <v>6000480</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2644553.98</v>
+        <v>1751123.58</v>
       </c>
       <c r="L8" t="n">
         <v>11271960</v>
@@ -20834,7 +20834,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4405922.88</v>
+        <v>2378418.55</v>
       </c>
       <c r="L9" t="n">
         <v>19184364</v>
@@ -20875,7 +20875,7 @@
         <v>97112</v>
       </c>
       <c r="K10" t="n">
-        <v>5111490.12</v>
+        <v>2196673.44</v>
       </c>
       <c r="L10" t="n">
         <v>22578588</v>
@@ -20916,7 +20916,7 @@
         <v>97112</v>
       </c>
       <c r="K11" t="n">
-        <v>5758838.71</v>
+        <v>2574026.39</v>
       </c>
       <c r="L11" t="n">
         <v>30294000</v>
@@ -20957,7 +20957,7 @@
         <v>169946</v>
       </c>
       <c r="K12" t="n">
-        <v>7426882.98</v>
+        <v>2160547.78</v>
       </c>
       <c r="L12" t="n">
         <v>33015600</v>
@@ -20998,7 +20998,7 @@
         <v>121390</v>
       </c>
       <c r="K13" t="n">
-        <v>9128576.560000001</v>
+        <v>2259092.18</v>
       </c>
       <c r="L13" t="n">
         <v>41617800</v>
@@ -21039,7 +21039,7 @@
         <v>48556</v>
       </c>
       <c r="K14" t="n">
-        <v>10147232.88</v>
+        <v>2973375.22</v>
       </c>
       <c r="L14" t="n">
         <v>45144000</v>
@@ -21080,7 +21080,7 @@
         <v>121390</v>
       </c>
       <c r="K15" t="n">
-        <v>10628519.95</v>
+        <v>2872572.96</v>
       </c>
       <c r="L15" t="n">
         <v>38021400</v>
@@ -21121,7 +21121,7 @@
         <v>48556</v>
       </c>
       <c r="K16" t="n">
-        <v>5146936</v>
+        <v>825452</v>
       </c>
       <c r="L16" t="n">
         <v>15849000</v>
@@ -21162,7 +21162,7 @@
         <v>48556</v>
       </c>
       <c r="K17" t="n">
-        <v>2039352</v>
+        <v>145668</v>
       </c>
       <c r="L17" t="n">
         <v>6717600</v>
@@ -21203,7 +21203,7 @@
         <v>24278</v>
       </c>
       <c r="K18" t="n">
-        <v>582672</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>2041200</v>
@@ -21244,7 +21244,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>988200</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>318600</v>
@@ -21326,7 +21326,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>135000</v>
@@ -21633,7 +21633,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="L4" t="n">
         <v>199740</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
         <v>344370</v>
@@ -21715,7 +21715,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>211</v>
+        <v>63</v>
       </c>
       <c r="L6" t="n">
         <v>257580</v>
@@ -21756,7 +21756,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="L7" t="n">
         <v>193530</v>
@@ -21797,7 +21797,7 @@
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>151320</v>
@@ -21838,7 +21838,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
         <v>68940</v>
@@ -21879,7 +21879,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>92040</v>
@@ -21920,7 +21920,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>43050</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>112.87</v>
+        <v>28.47</v>
       </c>
       <c r="L5" t="n">
         <v>72317.7</v>
@@ -22719,7 +22719,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>106.98</v>
+        <v>31.94</v>
       </c>
       <c r="L6" t="n">
         <v>95304.60000000001</v>
@@ -22760,7 +22760,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>117.39</v>
+        <v>30.62</v>
       </c>
       <c r="L7" t="n">
         <v>116118</v>
@@ -22801,7 +22801,7 @@
         <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>78.75</v>
+        <v>24.29</v>
       </c>
       <c r="L8" t="n">
         <v>107437.2</v>
@@ -22842,7 +22842,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>49.79</v>
+        <v>15.26</v>
       </c>
       <c r="L9" t="n">
         <v>55841.4</v>
@@ -22883,7 +22883,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>61.77</v>
+        <v>11.31</v>
       </c>
       <c r="L10" t="n">
         <v>81915.60000000001</v>
@@ -22924,7 +22924,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>25.16</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>43050</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5480564.28</v>
+        <v>1382195.1</v>
       </c>
       <c r="L5" t="n">
         <v>13017186</v>
@@ -23723,7 +23723,7 @@
         <v>157807</v>
       </c>
       <c r="K6" t="n">
-        <v>5194375.21</v>
+        <v>1550927.2</v>
       </c>
       <c r="L6" t="n">
         <v>17154828</v>
@@ -23764,7 +23764,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5700085.95</v>
+        <v>1486978.94</v>
       </c>
       <c r="L7" t="n">
         <v>20901240</v>
@@ -23805,7 +23805,7 @@
         <v>123817.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3823882.11</v>
+        <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
         <v>19338696</v>
@@ -23846,7 +23846,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2417409.02</v>
+        <v>740818.89</v>
       </c>
       <c r="L9" t="n">
         <v>10051452</v>
@@ -23887,7 +23887,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2999304.12</v>
+        <v>549168.36</v>
       </c>
       <c r="L10" t="n">
         <v>14744808</v>
@@ -23928,7 +23928,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1221571.85</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
         <v>7749000</v>
